--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/123.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/123.xlsx
@@ -426,13 +426,13 @@
         <v>-17.21272030369491</v>
       </c>
       <c r="E2">
-        <v>-4.984144724451774</v>
+        <v>-4.171315339392998</v>
       </c>
       <c r="F2">
-        <v>-2.076041928783973</v>
+        <v>-2.606136805388034</v>
       </c>
       <c r="G2">
-        <v>-7.826418822967336</v>
+        <v>-7.050357427105846</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.20203774894315</v>
       </c>
       <c r="E3">
-        <v>-4.848190877793495</v>
+        <v>-6.107278733938145</v>
       </c>
       <c r="F3">
-        <v>-2.031752009152793</v>
+        <v>-2.739840385446051</v>
       </c>
       <c r="G3">
-        <v>-7.164971824220953</v>
+        <v>-6.770328311575514</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.15665635416789</v>
       </c>
       <c r="E4">
-        <v>-6.545893140899073</v>
+        <v>-3.700480839867496</v>
       </c>
       <c r="F4">
-        <v>-1.845313397669515</v>
+        <v>-2.202359104452381</v>
       </c>
       <c r="G4">
-        <v>-6.556162499548982</v>
+        <v>-6.876080378281992</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.0203693900228</v>
       </c>
       <c r="E5">
-        <v>-5.748360941038208</v>
+        <v>-6.534848192794365</v>
       </c>
       <c r="F5">
-        <v>-1.880087620307777</v>
+        <v>-2.195395549542194</v>
       </c>
       <c r="G5">
-        <v>-6.935392112163576</v>
+        <v>-6.936219748548393</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.75262278585887</v>
       </c>
       <c r="E6">
-        <v>-6.788651047028258</v>
+        <v>-6.307627480985497</v>
       </c>
       <c r="F6">
-        <v>-1.431491041965187</v>
+        <v>-2.258537904390765</v>
       </c>
       <c r="G6">
-        <v>-6.995435476609337</v>
+        <v>-6.408445957586702</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.31941746138906</v>
       </c>
       <c r="E7">
-        <v>-7.932090733965024</v>
+        <v>-7.552160821669496</v>
       </c>
       <c r="F7">
-        <v>-1.309017520553551</v>
+        <v>-1.824548637559231</v>
       </c>
       <c r="G7">
-        <v>-6.767441515865269</v>
+        <v>-6.113569045312738</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.72071182411032</v>
       </c>
       <c r="E8">
-        <v>-8.546695226286044</v>
+        <v>-8.702361520299712</v>
       </c>
       <c r="F8">
-        <v>-1.346003388502724</v>
+        <v>-1.946303156485258</v>
       </c>
       <c r="G8">
-        <v>-6.488395632360101</v>
+        <v>-5.827988144913049</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.98149242592283</v>
       </c>
       <c r="E9">
-        <v>-9.485158065739618</v>
+        <v>-8.84830970909292</v>
       </c>
       <c r="F9">
-        <v>-1.297485765930279</v>
+        <v>-1.27606614342396</v>
       </c>
       <c r="G9">
-        <v>-5.540212352820823</v>
+        <v>-6.114141769691033</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.13896697936281</v>
       </c>
       <c r="E10">
-        <v>-10.59750977861373</v>
+        <v>-10.48386772339124</v>
       </c>
       <c r="F10">
-        <v>-1.173483968310243</v>
+        <v>-1.343288124710703</v>
       </c>
       <c r="G10">
-        <v>-6.032503716692605</v>
+        <v>-4.443666974939106</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.25872758137431</v>
       </c>
       <c r="E11">
-        <v>-10.79785399718707</v>
+        <v>-10.58111217423195</v>
       </c>
       <c r="F11">
-        <v>-1.179642208762429</v>
+        <v>-1.619343902830953</v>
       </c>
       <c r="G11">
-        <v>-4.664281729676138</v>
+        <v>-5.416460850017327</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.41899668850243</v>
       </c>
       <c r="E12">
-        <v>-11.45166148899249</v>
+        <v>-11.02011602995754</v>
       </c>
       <c r="F12">
-        <v>-1.174524463096687</v>
+        <v>-1.556481863929415</v>
       </c>
       <c r="G12">
-        <v>-3.960231320384874</v>
+        <v>-4.504067878303109</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.68680883781692</v>
       </c>
       <c r="E13">
-        <v>-12.49815107589905</v>
+        <v>-11.74610739744523</v>
       </c>
       <c r="F13">
-        <v>-1.116026325845142</v>
+        <v>-1.121465563811719</v>
       </c>
       <c r="G13">
-        <v>-3.59913025514333</v>
+        <v>-4.408826793683816</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.12565917913161</v>
       </c>
       <c r="E14">
-        <v>-13.73145832951803</v>
+        <v>-13.26296505105449</v>
       </c>
       <c r="F14">
-        <v>-1.002869746334036</v>
+        <v>-0.8020352480794133</v>
       </c>
       <c r="G14">
-        <v>-2.913539447779042</v>
+        <v>-3.120627313442612</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.77055737754479</v>
       </c>
       <c r="E15">
-        <v>-13.72031828345916</v>
+        <v>-13.81774840173419</v>
       </c>
       <c r="F15">
-        <v>-1.287665997401596</v>
+        <v>-0.86650554033808</v>
       </c>
       <c r="G15">
-        <v>-2.588284969636726</v>
+        <v>-2.42446924471697</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.61073371379423</v>
       </c>
       <c r="E16">
-        <v>-14.3473896647233</v>
+        <v>-15.02365838760676</v>
       </c>
       <c r="F16">
-        <v>-0.569053895300243</v>
+        <v>-0.9583684019631452</v>
       </c>
       <c r="G16">
-        <v>-1.425396259148015</v>
+        <v>-2.625406116768574</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.61168529408897</v>
       </c>
       <c r="E17">
-        <v>-15.15872465335954</v>
+        <v>-14.92645922150613</v>
       </c>
       <c r="F17">
-        <v>-0.6823371712845844</v>
+        <v>-0.4765369631321014</v>
       </c>
       <c r="G17">
-        <v>-0.8769911483855856</v>
+        <v>-1.543595977082153</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.7190545646858</v>
       </c>
       <c r="E18">
-        <v>-16.69925716908091</v>
+        <v>-15.83273819618719</v>
       </c>
       <c r="F18">
-        <v>-0.4211531835632685</v>
+        <v>-0.489147221483788</v>
       </c>
       <c r="G18">
-        <v>-0.3741821813355384</v>
+        <v>-0.915390166095592</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.86495102461738</v>
       </c>
       <c r="E19">
-        <v>-17.33587457355321</v>
+        <v>-16.3388268658624</v>
       </c>
       <c r="F19">
-        <v>-0.4085983549186222</v>
+        <v>-0.05173239875715892</v>
       </c>
       <c r="G19">
-        <v>0.1699357729535347</v>
+        <v>0.6055472866474553</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.99523603051062</v>
       </c>
       <c r="E20">
-        <v>-18.52416879553595</v>
+        <v>-18.30132258961849</v>
       </c>
       <c r="F20">
-        <v>-0.2877726795120005</v>
+        <v>0.4722937167789381</v>
       </c>
       <c r="G20">
-        <v>0.4345013302699308</v>
+        <v>-0.2634742279567706</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.07077879932128</v>
       </c>
       <c r="E21">
-        <v>-18.74694707434329</v>
+        <v>-18.57519564065438</v>
       </c>
       <c r="F21">
-        <v>-0.111590939390066</v>
+        <v>0.4134566664614894</v>
       </c>
       <c r="G21">
-        <v>1.345487320129958</v>
+        <v>0.1911960964067342</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.06500745594408</v>
       </c>
       <c r="E22">
-        <v>-19.34943337021979</v>
+        <v>-19.7945325519597</v>
       </c>
       <c r="F22">
-        <v>-0.01705399032678134</v>
+        <v>0.9430843498204958</v>
       </c>
       <c r="G22">
-        <v>0.6506865750754179</v>
+        <v>0.4212690797494639</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.97412113363435</v>
       </c>
       <c r="E23">
-        <v>-19.24809970735015</v>
+        <v>-18.79340921766199</v>
       </c>
       <c r="F23">
-        <v>0.6649364961859502</v>
+        <v>0.5644994507346959</v>
       </c>
       <c r="G23">
-        <v>1.753277009111844</v>
+        <v>0.05682767405879528</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.81058539084159</v>
       </c>
       <c r="E24">
-        <v>-19.68943572718969</v>
+        <v>-19.58317961307371</v>
       </c>
       <c r="F24">
-        <v>0.4731813839445419</v>
+        <v>0.7321949027087481</v>
       </c>
       <c r="G24">
-        <v>1.340554607276444</v>
+        <v>0.6208684914032023</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.59491919612286</v>
       </c>
       <c r="E25">
-        <v>-20.20334959995016</v>
+        <v>-19.63596803458112</v>
       </c>
       <c r="F25">
-        <v>0.6075477449281709</v>
+        <v>0.7261308927585304</v>
       </c>
       <c r="G25">
-        <v>1.286334492434261</v>
+        <v>0.2705366308009075</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.35407069423411</v>
       </c>
       <c r="E26">
-        <v>-20.51070618779876</v>
+        <v>-20.56747513795892</v>
       </c>
       <c r="F26">
-        <v>0.1921163440137568</v>
+        <v>0.6935809850785035</v>
       </c>
       <c r="G26">
-        <v>1.582360164010351</v>
+        <v>1.057896918587931</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.11706960858087</v>
       </c>
       <c r="E27">
-        <v>-21.03350039808827</v>
+        <v>-20.62516336834263</v>
       </c>
       <c r="F27">
-        <v>0.3991201686619739</v>
+        <v>0.3208550060268718</v>
       </c>
       <c r="G27">
-        <v>1.190931191083544</v>
+        <v>-0.3502668003598433</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.905407250108299</v>
       </c>
       <c r="E28">
-        <v>-20.79407092035472</v>
+        <v>-21.14512275390334</v>
       </c>
       <c r="F28">
-        <v>0.5078407879039342</v>
+        <v>0.8838299929943289</v>
       </c>
       <c r="G28">
-        <v>0.5183541382341308</v>
+        <v>0.4327831571350491</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.731465293718257</v>
       </c>
       <c r="E29">
-        <v>-21.07013575281033</v>
+        <v>-20.29470250610689</v>
       </c>
       <c r="F29">
-        <v>0.6523286133931367</v>
+        <v>0.7795762162868655</v>
       </c>
       <c r="G29">
-        <v>0.7659928762082333</v>
+        <v>-0.06996622009529119</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.602990003471191</v>
       </c>
       <c r="E30">
-        <v>-20.61506939977953</v>
+        <v>-19.70308907632282</v>
       </c>
       <c r="F30">
-        <v>0.6013776266816189</v>
+        <v>0.4672939572038958</v>
       </c>
       <c r="G30">
-        <v>0.3778512750019223</v>
+        <v>0.02817490241640316</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.521477416151699</v>
       </c>
       <c r="E31">
-        <v>-20.93388755534155</v>
+        <v>-20.66674834515506</v>
       </c>
       <c r="F31">
-        <v>0.4431994554064</v>
+        <v>0.614853380316093</v>
       </c>
       <c r="G31">
-        <v>0.3423887111852493</v>
+        <v>-0.702025506089564</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.483372489203322</v>
       </c>
       <c r="E32">
-        <v>-19.89862858397402</v>
+        <v>-18.55745760796633</v>
       </c>
       <c r="F32">
-        <v>0.4488691225836732</v>
+        <v>0.5692489847750988</v>
       </c>
       <c r="G32">
-        <v>-0.2635834759595665</v>
+        <v>-0.2725749176442271</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.484337778262308</v>
       </c>
       <c r="E33">
-        <v>-19.98982299354049</v>
+        <v>-18.4999324026469</v>
       </c>
       <c r="F33">
-        <v>0.7029771122748057</v>
+        <v>0.7000900163909596</v>
       </c>
       <c r="G33">
-        <v>-0.5420996721784516</v>
+        <v>0.1686247969199833</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.51530956300539</v>
       </c>
       <c r="E34">
-        <v>-19.54660765698776</v>
+        <v>-18.60575831173215</v>
       </c>
       <c r="F34">
-        <v>0.7327887924270379</v>
+        <v>0.8378930192110923</v>
       </c>
       <c r="G34">
-        <v>-0.6690259881541089</v>
+        <v>-0.3235904244043961</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.560928279052808</v>
       </c>
       <c r="E35">
-        <v>-18.90035365982714</v>
+        <v>-18.37462499838065</v>
       </c>
       <c r="F35">
-        <v>0.673779910017764</v>
+        <v>0.5868360389660539</v>
       </c>
       <c r="G35">
-        <v>-0.8920640622258873</v>
+        <v>-1.004079681092667</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.60663433617872</v>
       </c>
       <c r="E36">
-        <v>-17.91979412599826</v>
+        <v>-17.62737697390096</v>
       </c>
       <c r="F36">
-        <v>0.9915362485974503</v>
+        <v>1.0016450434557</v>
       </c>
       <c r="G36">
-        <v>-1.289216968390094</v>
+        <v>-1.312549693350878</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.639597674141051</v>
       </c>
       <c r="E37">
-        <v>-17.24901391361209</v>
+        <v>-17.18153059394978</v>
       </c>
       <c r="F37">
-        <v>0.6173112918968551</v>
+        <v>1.068705486739068</v>
       </c>
       <c r="G37">
-        <v>-1.008737618666422</v>
+        <v>-1.218146176753021</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.646346116777778</v>
       </c>
       <c r="E38">
-        <v>-16.93882702950869</v>
+        <v>-17.90395352391943</v>
       </c>
       <c r="F38">
-        <v>0.925635078044184</v>
+        <v>0.9075808306081743</v>
       </c>
       <c r="G38">
-        <v>-1.609800266776498</v>
+        <v>-1.5345714299421</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.620078671530964</v>
       </c>
       <c r="E39">
-        <v>-16.25178506696097</v>
+        <v>-16.80646426273849</v>
       </c>
       <c r="F39">
-        <v>1.112596312479557</v>
+        <v>1.203985646035906</v>
       </c>
       <c r="G39">
-        <v>-1.698191832675039</v>
+        <v>-1.704521595746126</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.561761714522753</v>
       </c>
       <c r="E40">
-        <v>-17.5472229839652</v>
+        <v>-15.68212567916608</v>
       </c>
       <c r="F40">
-        <v>1.142388988160804</v>
+        <v>1.216636288888436</v>
       </c>
       <c r="G40">
-        <v>-1.515029279623782</v>
+        <v>-0.6956196004710743</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.473894667215202</v>
       </c>
       <c r="E41">
-        <v>-15.59229434027592</v>
+        <v>-15.51315472851788</v>
       </c>
       <c r="F41">
-        <v>1.317226953813488</v>
+        <v>1.263588418163469</v>
       </c>
       <c r="G41">
-        <v>-1.507103833602767</v>
+        <v>-1.29505014963029</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.365953891147104</v>
       </c>
       <c r="E42">
-        <v>-15.57695187033794</v>
+        <v>-15.21580606822623</v>
       </c>
       <c r="F42">
-        <v>1.012051575026053</v>
+        <v>0.9333429747346277</v>
       </c>
       <c r="G42">
-        <v>-2.254118502902692</v>
+        <v>-0.8147826871571406</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.254975621199378</v>
       </c>
       <c r="E43">
-        <v>-13.80553963580951</v>
+        <v>-15.07595320544734</v>
       </c>
       <c r="F43">
-        <v>0.9634523915989625</v>
+        <v>1.284094242356579</v>
       </c>
       <c r="G43">
-        <v>-1.56727630932456</v>
+        <v>-1.304733495332659</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.153523796173877</v>
       </c>
       <c r="E44">
-        <v>-12.71754205614865</v>
+        <v>-14.04487401558889</v>
       </c>
       <c r="F44">
-        <v>1.399848891421964</v>
+        <v>0.7849624001052751</v>
       </c>
       <c r="G44">
-        <v>-1.600063952345502</v>
+        <v>-2.062136656534817</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.075343037129638</v>
       </c>
       <c r="E45">
-        <v>-13.74707703637048</v>
+        <v>-12.40575209224654</v>
       </c>
       <c r="F45">
-        <v>1.526624549952892</v>
+        <v>0.9421753026250336</v>
       </c>
       <c r="G45">
-        <v>-1.202808419269577</v>
+        <v>-1.24631229820114</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.038459164853755</v>
       </c>
       <c r="E46">
-        <v>-13.31022420579854</v>
+        <v>-12.52807976061574</v>
       </c>
       <c r="F46">
-        <v>1.222355050949088</v>
+        <v>0.8234923813220013</v>
       </c>
       <c r="G46">
-        <v>-0.6147032464002079</v>
+        <v>-0.9217596557131498</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.051041701403456</v>
       </c>
       <c r="E47">
-        <v>-12.83902742835242</v>
+        <v>-12.66340867786096</v>
       </c>
       <c r="F47">
-        <v>1.292524308944464</v>
+        <v>0.9848593444579575</v>
       </c>
       <c r="G47">
-        <v>-1.438966185313487</v>
+        <v>-1.651758120941222</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.120587934529011</v>
       </c>
       <c r="E48">
-        <v>-11.25879830947982</v>
+        <v>-12.35431315599341</v>
       </c>
       <c r="F48">
-        <v>1.387397795514779</v>
+        <v>0.8775680198046812</v>
       </c>
       <c r="G48">
-        <v>-0.9992330424231741</v>
+        <v>-1.56459807798329</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.259349598235827</v>
       </c>
       <c r="E49">
-        <v>-10.53916039102489</v>
+        <v>-11.06037869235974</v>
       </c>
       <c r="F49">
-        <v>1.291946256285328</v>
+        <v>0.9997335104157649</v>
       </c>
       <c r="G49">
-        <v>-0.1383654014821732</v>
+        <v>-1.21101526166143</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.468679902027901</v>
       </c>
       <c r="E50">
-        <v>-10.98733893509002</v>
+        <v>-8.915177156290181</v>
       </c>
       <c r="F50">
-        <v>1.070949598021246</v>
+        <v>0.8492830321549327</v>
       </c>
       <c r="G50">
-        <v>-1.373241924722336</v>
+        <v>-1.115376911577425</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.748015145629164</v>
       </c>
       <c r="E51">
-        <v>-9.247372424070855</v>
+        <v>-10.14507446898139</v>
       </c>
       <c r="F51">
-        <v>1.358517334440825</v>
+        <v>0.9178115708219131</v>
       </c>
       <c r="G51">
-        <v>-0.6693371794348003</v>
+        <v>-0.3708252881587174</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.10161775075691</v>
       </c>
       <c r="E52">
-        <v>-10.31313519635405</v>
+        <v>-9.258942675160453</v>
       </c>
       <c r="F52">
-        <v>1.160197761179921</v>
+        <v>1.210329971933156</v>
       </c>
       <c r="G52">
-        <v>-1.192310679364548</v>
+        <v>-0.5811343146319981</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.52227875406488</v>
       </c>
       <c r="E53">
-        <v>-8.729238013535236</v>
+        <v>-10.19444842108702</v>
       </c>
       <c r="F53">
-        <v>1.329621036307717</v>
+        <v>0.884309855886707</v>
       </c>
       <c r="G53">
-        <v>-1.184656698077753</v>
+        <v>-0.2820530095231605</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.00190315696956</v>
       </c>
       <c r="E54">
-        <v>-8.085365993702641</v>
+        <v>-9.110752891733448</v>
       </c>
       <c r="F54">
-        <v>1.224841469236328</v>
+        <v>0.9317893592315817</v>
       </c>
       <c r="G54">
-        <v>-1.025548568914841</v>
+        <v>-2.047980763808893</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.54021547129519</v>
       </c>
       <c r="E55">
-        <v>-8.183190089216337</v>
+        <v>-8.11116471012434</v>
       </c>
       <c r="F55">
-        <v>1.166123988715495</v>
+        <v>0.7386516717259947</v>
       </c>
       <c r="G55">
-        <v>-1.014133807895434</v>
+        <v>0.01071177469674765</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.12710592267895</v>
       </c>
       <c r="E56">
-        <v>-7.506577202308286</v>
+        <v>-8.852693271932345</v>
       </c>
       <c r="F56">
-        <v>1.272729568707386</v>
+        <v>1.102755163921016</v>
       </c>
       <c r="G56">
-        <v>-1.629458286188691</v>
+        <v>-1.194922699795033</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.75144299036947</v>
       </c>
       <c r="E57">
-        <v>-6.634986338525979</v>
+        <v>-7.792677133164884</v>
       </c>
       <c r="F57">
-        <v>1.622899616258371</v>
+        <v>0.5145572846913129</v>
       </c>
       <c r="G57">
-        <v>-1.143748286848979</v>
+        <v>-0.8410286921924827</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.4093738092364</v>
       </c>
       <c r="E58">
-        <v>-7.598912787324684</v>
+        <v>-7.185920486299155</v>
       </c>
       <c r="F58">
-        <v>1.311123351215384</v>
+        <v>0.8562956819484986</v>
       </c>
       <c r="G58">
-        <v>-1.941943990186037</v>
+        <v>-1.884568925444928</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.08663178741306</v>
       </c>
       <c r="E59">
-        <v>-6.426830502289404</v>
+        <v>-6.614354610947033</v>
       </c>
       <c r="F59">
-        <v>1.562191417401831</v>
+        <v>0.7102574083680808</v>
       </c>
       <c r="G59">
-        <v>-1.338563960198471</v>
+        <v>-1.833384580862257</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.76797389524802</v>
       </c>
       <c r="E60">
-        <v>-6.703606305164208</v>
+        <v>-6.453199806436069</v>
       </c>
       <c r="F60">
-        <v>1.235206824452879</v>
+        <v>1.032239074330159</v>
       </c>
       <c r="G60">
-        <v>-1.933882811797912</v>
+        <v>-1.149707268819667</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.44627907760442</v>
       </c>
       <c r="E61">
-        <v>-6.601063539734521</v>
+        <v>-5.826300507184222</v>
       </c>
       <c r="F61">
-        <v>1.176231199867829</v>
+        <v>0.7724416211378108</v>
       </c>
       <c r="G61">
-        <v>-2.133329938356844</v>
+        <v>-0.9864609577326658</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.10556427717027</v>
       </c>
       <c r="E62">
-        <v>-5.295255417252735</v>
+        <v>-6.446796544189223</v>
       </c>
       <c r="F62">
-        <v>1.491325328803662</v>
+        <v>0.7227766036296297</v>
       </c>
       <c r="G62">
-        <v>-2.779902655995282</v>
+        <v>-1.988069821184703</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.73009090109838</v>
       </c>
       <c r="E63">
-        <v>-5.70409510761323</v>
+        <v>-6.336147810285805</v>
       </c>
       <c r="F63">
-        <v>1.304449614487723</v>
+        <v>0.9810378620840021</v>
       </c>
       <c r="G63">
-        <v>-2.565177361772613</v>
+        <v>-3.266612440087853</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.31068002911138</v>
       </c>
       <c r="E64">
-        <v>-4.677299854166038</v>
+        <v>-4.833699760968949</v>
       </c>
       <c r="F64">
-        <v>1.310228557373161</v>
+        <v>0.6999015553870223</v>
       </c>
       <c r="G64">
-        <v>-2.29691723563439</v>
+        <v>-2.206612174414151</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.83034063657295</v>
       </c>
       <c r="E65">
-        <v>-4.923254862944638</v>
+        <v>-4.92344505885296</v>
       </c>
       <c r="F65">
-        <v>1.180928471613023</v>
+        <v>0.7857447508275021</v>
       </c>
       <c r="G65">
-        <v>-2.804106054432893</v>
+        <v>-2.763042047563773</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.27488070358254</v>
       </c>
       <c r="E66">
-        <v>-4.506730352193126</v>
+        <v>-4.940970253262645</v>
       </c>
       <c r="F66">
-        <v>1.225951647083051</v>
+        <v>0.7921825153737635</v>
       </c>
       <c r="G66">
-        <v>-3.308626573526744</v>
+        <v>-2.387920821963416</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.63892886676309</v>
       </c>
       <c r="E67">
-        <v>-4.525437478318812</v>
+        <v>-3.63273034023874</v>
       </c>
       <c r="F67">
-        <v>1.087871495727716</v>
+        <v>0.465004710303128</v>
       </c>
       <c r="G67">
-        <v>-3.885081936643417</v>
+        <v>-3.493133208066945</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.91337741594998</v>
       </c>
       <c r="E68">
-        <v>-4.671806815194734</v>
+        <v>-4.070778687948708</v>
       </c>
       <c r="F68">
-        <v>0.6199893385998633</v>
+        <v>0.05254750909790921</v>
       </c>
       <c r="G68">
-        <v>-3.623760713955507</v>
+        <v>-2.824350040405537</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-19.09413407446075</v>
       </c>
       <c r="E69">
-        <v>-5.282743243569541</v>
+        <v>-5.291895289539044</v>
       </c>
       <c r="F69">
-        <v>0.5941622625308767</v>
+        <v>0.6730862468268016</v>
       </c>
       <c r="G69">
-        <v>-3.600964297372086</v>
+        <v>-2.763846510129816</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-19.18522262203129</v>
       </c>
       <c r="E70">
-        <v>-5.376518883320379</v>
+        <v>-4.253267133509809</v>
       </c>
       <c r="F70">
-        <v>0.7788999738609729</v>
+        <v>0.2759078484407849</v>
       </c>
       <c r="G70">
-        <v>-3.464195729508175</v>
+        <v>-2.300436345542636</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-19.18659079481126</v>
       </c>
       <c r="E71">
-        <v>-4.903388447472988</v>
+        <v>-4.606710001334473</v>
       </c>
       <c r="F71">
-        <v>0.1411495202430846</v>
+        <v>0.2170090335926341</v>
       </c>
       <c r="G71">
-        <v>-2.76573683163274</v>
+        <v>-2.615563864880321</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-19.10238967204053</v>
       </c>
       <c r="E72">
-        <v>-5.350190335439784</v>
+        <v>-5.078164901799026</v>
       </c>
       <c r="F72">
-        <v>0.1304436682547139</v>
+        <v>-0.05107357709633611</v>
       </c>
       <c r="G72">
-        <v>-3.846173094920363</v>
+        <v>-2.402500464518366</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.94367981275372</v>
       </c>
       <c r="E73">
-        <v>-4.646646613608118</v>
+        <v>-4.315189487090693</v>
       </c>
       <c r="F73">
-        <v>0.4944252150942466</v>
+        <v>0.421060830414472</v>
       </c>
       <c r="G73">
-        <v>-3.055532056503922</v>
+        <v>-2.435543019545832</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.71755941876107</v>
       </c>
       <c r="E74">
-        <v>-4.793418984670721</v>
+        <v>-4.771292860669244</v>
       </c>
       <c r="F74">
-        <v>0.4467920922755744</v>
+        <v>0.2920774858374216</v>
       </c>
       <c r="G74">
-        <v>-2.95978776896266</v>
+        <v>-1.687396143671476</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.43390177793672</v>
       </c>
       <c r="E75">
-        <v>-5.966760185480134</v>
+        <v>-6.589457060852862</v>
       </c>
       <c r="F75">
-        <v>0.593251631629499</v>
+        <v>-0.1230324227761583</v>
       </c>
       <c r="G75">
-        <v>-2.914886839813525</v>
+        <v>-1.831292316081437</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.10835109079824</v>
       </c>
       <c r="E76">
-        <v>-5.988130054322331</v>
+        <v>-6.196480614941236</v>
       </c>
       <c r="F76">
-        <v>0.1838549421058669</v>
+        <v>-0.305988464951385</v>
       </c>
       <c r="G76">
-        <v>-2.973725165682992</v>
+        <v>-2.788457105668758</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.75270456864864</v>
       </c>
       <c r="E77">
-        <v>-6.437617327375674</v>
+        <v>-6.610763531058951</v>
       </c>
       <c r="F77">
-        <v>-0.1918381099783405</v>
+        <v>-0.04337755820025812</v>
       </c>
       <c r="G77">
-        <v>-2.679609678883061</v>
+        <v>-2.417384677262929</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.37952388830226</v>
       </c>
       <c r="E78">
-        <v>-6.446538421170786</v>
+        <v>-6.727204183218179</v>
       </c>
       <c r="F78">
-        <v>0.2700940640252066</v>
+        <v>-0.256289397766022</v>
       </c>
       <c r="G78">
-        <v>-2.744648656547583</v>
+        <v>-2.284178256399275</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.00495056240193</v>
       </c>
       <c r="E79">
-        <v>-6.765293178096695</v>
+        <v>-8.381387811110045</v>
       </c>
       <c r="F79">
-        <v>-0.2250682193490487</v>
+        <v>-0.5562124158849022</v>
       </c>
       <c r="G79">
-        <v>-3.225680855040304</v>
+        <v>-2.085171432397066</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.63925133189414</v>
       </c>
       <c r="E80">
-        <v>-7.907256582506959</v>
+        <v>-8.230829635777029</v>
       </c>
       <c r="F80">
-        <v>0.03468489007766769</v>
+        <v>-0.2014599152675929</v>
       </c>
       <c r="G80">
-        <v>-1.893563677675128</v>
+        <v>-1.619165800107097</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.2887446682052</v>
       </c>
       <c r="E81">
-        <v>-9.496243770110395</v>
+        <v>-9.590906990766737</v>
       </c>
       <c r="F81">
-        <v>0.1076367193664704</v>
+        <v>-0.9030321335717755</v>
       </c>
       <c r="G81">
-        <v>-2.333905960944668</v>
+        <v>-0.9791479626364158</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.96113018807824</v>
       </c>
       <c r="E82">
-        <v>-9.729174887642936</v>
+        <v>-9.178000730747353</v>
       </c>
       <c r="F82">
-        <v>-0.2261182163709851</v>
+        <v>-0.4865776586359875</v>
       </c>
       <c r="G82">
-        <v>-2.27475313324897</v>
+        <v>-1.359589234918382</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.65932834426754</v>
       </c>
       <c r="E83">
-        <v>-10.48214690326832</v>
+        <v>-11.10945376518086</v>
       </c>
       <c r="F83">
-        <v>-0.3592128615045163</v>
+        <v>-0.4325978343611916</v>
       </c>
       <c r="G83">
-        <v>-2.280116217022589</v>
+        <v>-0.999574028613719</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-15.3823490534715</v>
       </c>
       <c r="E84">
-        <v>-11.48040371351918</v>
+        <v>-11.260084396098</v>
       </c>
       <c r="F84">
-        <v>-0.4074050325113386</v>
+        <v>-0.9587872921777789</v>
       </c>
       <c r="G84">
-        <v>-1.245064222532835</v>
+        <v>-0.8335766541835832</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-15.13317956560256</v>
       </c>
       <c r="E85">
-        <v>-12.83466197940903</v>
+        <v>-13.30747089360188</v>
       </c>
       <c r="F85">
-        <v>-0.5837253469008741</v>
+        <v>-0.9289558157016038</v>
       </c>
       <c r="G85">
-        <v>-2.162545502740912</v>
+        <v>-0.4820099600951402</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.91418009087999</v>
       </c>
       <c r="E86">
-        <v>-13.36694334274461</v>
+        <v>-13.40987327633733</v>
       </c>
       <c r="F86">
-        <v>-0.2025265412016413</v>
+        <v>-0.801762058809</v>
       </c>
       <c r="G86">
-        <v>-1.484135268651303</v>
+        <v>-1.187778542521286</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.72248558426844</v>
       </c>
       <c r="E87">
-        <v>-14.98561467746832</v>
+        <v>-16.40173189830296</v>
       </c>
       <c r="F87">
-        <v>-1.02161369769622</v>
+        <v>-0.9399182280482756</v>
       </c>
       <c r="G87">
-        <v>-1.42173810632712</v>
+        <v>-0.2412174302962504</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.56045903574813</v>
       </c>
       <c r="E88">
-        <v>-16.3679902384718</v>
+        <v>-16.15437759105598</v>
       </c>
       <c r="F88">
-        <v>-0.7488282722913518</v>
+        <v>-1.113345903583261</v>
       </c>
       <c r="G88">
-        <v>-1.032285529087258</v>
+        <v>-0.06022659511875535</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.43529415451702</v>
       </c>
       <c r="E89">
-        <v>-17.39589496805088</v>
+        <v>-18.20887832122591</v>
       </c>
       <c r="F89">
-        <v>-0.9856176459441963</v>
+        <v>-1.062148650601892</v>
       </c>
       <c r="G89">
-        <v>-0.9401033885462514</v>
+        <v>-0.5130992932544359</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.34942128094078</v>
       </c>
       <c r="E90">
-        <v>-19.21618755101809</v>
+        <v>-19.81255587851023</v>
       </c>
       <c r="F90">
-        <v>-1.046936363431139</v>
+        <v>-1.361128571848128</v>
       </c>
       <c r="G90">
-        <v>-0.6190764770575852</v>
+        <v>0.4748138433016361</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.31000929760646</v>
       </c>
       <c r="E91">
-        <v>-21.42448884391053</v>
+        <v>-20.69326256046998</v>
       </c>
       <c r="F91">
-        <v>-1.088915656131692</v>
+        <v>-1.771762135691719</v>
       </c>
       <c r="G91">
-        <v>-0.9057366153030773</v>
+        <v>-0.2489939017679984</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.32827204829056</v>
       </c>
       <c r="E92">
-        <v>-23.18165449921083</v>
+        <v>-23.49316822619847</v>
       </c>
       <c r="F92">
-        <v>-1.610996188950672</v>
+        <v>-1.833117278414716</v>
       </c>
       <c r="G92">
-        <v>-1.114178494092209</v>
+        <v>0.287804436333746</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.40265159990905</v>
       </c>
       <c r="E93">
-        <v>-25.60497226646146</v>
+        <v>-25.53277933383118</v>
       </c>
       <c r="F93">
-        <v>-1.220956344978498</v>
+        <v>-2.122894284586333</v>
       </c>
       <c r="G93">
-        <v>-0.8104690463194703</v>
+        <v>0.5373301852652332</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.52871182042012</v>
       </c>
       <c r="E94">
-        <v>-27.12377263542001</v>
+        <v>-27.5333142392517</v>
       </c>
       <c r="F94">
-        <v>-2.088668024194814</v>
+        <v>-2.132898554854164</v>
       </c>
       <c r="G94">
-        <v>-0.6326927508606075</v>
+        <v>-0.1618702748109986</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.702762639095</v>
       </c>
       <c r="E95">
-        <v>-29.40030897466002</v>
+        <v>-29.55051166478344</v>
       </c>
       <c r="F95">
-        <v>-1.93682546843431</v>
+        <v>-2.212273103483032</v>
       </c>
       <c r="G95">
-        <v>-0.3319859678919878</v>
+        <v>0.4656138372480015</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.90552560585758</v>
       </c>
       <c r="E96">
-        <v>-32.17925686268102</v>
+        <v>-31.83497056929987</v>
       </c>
       <c r="F96">
-        <v>-1.949015252865448</v>
+        <v>-2.254618232250052</v>
       </c>
       <c r="G96">
-        <v>-0.3535078244427898</v>
+        <v>0.01459173406877348</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.11895390950161</v>
       </c>
       <c r="E97">
-        <v>-33.73048110553449</v>
+        <v>-35.56733431794777</v>
       </c>
       <c r="F97">
-        <v>-2.304356100230343</v>
+        <v>-2.353896796824162</v>
       </c>
       <c r="G97">
-        <v>-1.193631587034717</v>
+        <v>-1.11608205777729</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.33383931956512</v>
       </c>
       <c r="E98">
-        <v>-37.21874425550994</v>
+        <v>-35.92434335905347</v>
       </c>
       <c r="F98">
-        <v>-2.41662342886993</v>
+        <v>-2.378729305578252</v>
       </c>
       <c r="G98">
-        <v>-1.123073929956231</v>
+        <v>-0.2572338496152444</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.52904138729233</v>
       </c>
       <c r="E99">
-        <v>-39.8517258408417</v>
+        <v>-39.57517419743027</v>
       </c>
       <c r="F99">
-        <v>-2.368219041270438</v>
+        <v>-2.465502136391095</v>
       </c>
       <c r="G99">
-        <v>-1.4042948418807</v>
+        <v>-1.889372527022411</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-15.69215626558422</v>
       </c>
       <c r="E100">
-        <v>-42.64100997078521</v>
+        <v>-42.92194744127306</v>
       </c>
       <c r="F100">
-        <v>-2.453788255587547</v>
+        <v>-2.865478151276736</v>
       </c>
       <c r="G100">
-        <v>-1.656594827974097</v>
+        <v>-1.082178760909614</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.81555950330647</v>
       </c>
       <c r="E101">
-        <v>-44.56427099573884</v>
+        <v>-44.72906669335197</v>
       </c>
       <c r="F101">
-        <v>-2.959516232976657</v>
+        <v>-2.968567904136351</v>
       </c>
       <c r="G101">
-        <v>-1.825091664286382</v>
+        <v>-1.883814121061975</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.8913955772516</v>
       </c>
       <c r="E102">
-        <v>-46.75873780053784</v>
+        <v>-47.37085842486565</v>
       </c>
       <c r="F102">
-        <v>-2.853198095608418</v>
+        <v>-3.15658626227028</v>
       </c>
       <c r="G102">
-        <v>-2.372129519741093</v>
+        <v>-1.70572663432242</v>
       </c>
     </row>
   </sheetData>
